--- a/exports/trend_1d/BAJAJFINSV_full_report.xlsx
+++ b/exports/trend_1d/BAJAJFINSV_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42083</v>
+        <v>42086</v>
       </c>
       <c r="H2" t="n">
-        <v>138</v>
+        <v>133.55</v>
       </c>
       <c r="I2" t="n">
         <v>134.2312262434926</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K2" t="n">
-        <v>7.06</v>
+        <v>3.61</v>
       </c>
       <c r="L2" t="n">
         <v>2.95</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>17.09</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42150</v>
+        <v>42151</v>
       </c>
       <c r="H3" t="n">
-        <v>148.2</v>
+        <v>153.3</v>
       </c>
       <c r="I3" t="n">
         <v>148.2040538312226</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.97</v>
+        <v>-14.79</v>
       </c>
       <c r="L3" t="n">
-        <v>11.79</v>
+        <v>16.06</v>
       </c>
       <c r="M3" t="n">
         <v>1.3</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.39</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>187.8</v>
+        <v>171.45</v>
       </c>
       <c r="I4" t="n">
         <v>180.1716792454571</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K4" t="n">
-        <v>22.5</v>
+        <v>11.84</v>
       </c>
       <c r="L4" t="n">
         <v>6.39</v>
@@ -669,7 +716,7 @@
         <v>4.37</v>
       </c>
       <c r="N4" t="n">
-        <v>3.26</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>3.44</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>17.48</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42300</v>
+        <v>42303</v>
       </c>
       <c r="H5" t="n">
-        <v>182.95</v>
+        <v>190.55</v>
       </c>
       <c r="I5" t="n">
         <v>189.9126375015619</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.71</v>
+        <v>-11.14</v>
       </c>
       <c r="L5" t="n">
-        <v>11.69</v>
+        <v>11.93</v>
       </c>
       <c r="M5" t="n">
         <v>1.76</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.45</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42346</v>
+        <v>42347</v>
       </c>
       <c r="H6" t="n">
-        <v>191</v>
+        <v>187.4</v>
       </c>
       <c r="I6" t="n">
         <v>188.0901951548886</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" t="n">
-        <v>0.24</v>
+        <v>-1.65</v>
       </c>
       <c r="L6" t="n">
         <v>3.88</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.82</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42472</v>
+        <v>42473</v>
       </c>
       <c r="H7" t="n">
-        <v>177.85</v>
+        <v>182.1</v>
       </c>
       <c r="I7" t="n">
         <v>178.820485551623</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>2.83</v>
       </c>
       <c r="L7" t="n">
         <v>9.119999999999999</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42513</v>
+        <v>42514</v>
       </c>
       <c r="H8" t="n">
-        <v>180.6</v>
+        <v>176.2</v>
       </c>
       <c r="I8" t="n">
         <v>178.5283059996627</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.82</v>
+        <v>-3.24</v>
       </c>
       <c r="L8" t="n">
-        <v>2.97</v>
+        <v>5.24</v>
       </c>
       <c r="M8" t="n">
         <v>1.33</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>10.6</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42535</v>
+        <v>42536</v>
       </c>
       <c r="H9" t="n">
-        <v>187.4</v>
+        <v>194.7</v>
       </c>
       <c r="I9" t="n">
         <v>194.3128482874724</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.36</v>
+        <v>-10.5</v>
       </c>
       <c r="L9" t="n">
-        <v>9.02</v>
+        <v>10.78</v>
       </c>
       <c r="M9" t="n">
         <v>1.31</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.12</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42681</v>
+        <v>42682</v>
       </c>
       <c r="H10" t="n">
-        <v>314.15</v>
+        <v>307.2</v>
       </c>
       <c r="I10" t="n">
         <v>309.1506034776764</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K10" t="n">
-        <v>61.35</v>
+        <v>57.78</v>
       </c>
       <c r="L10" t="n">
         <v>3.44</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.59</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H11" t="n">
-        <v>289.5</v>
+        <v>294.95</v>
       </c>
       <c r="I11" t="n">
         <v>290.4971939037317</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K11" t="n">
-        <v>5.76</v>
+        <v>3.99</v>
       </c>
       <c r="L11" t="n">
         <v>3.78</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.63</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H12" t="n">
-        <v>431.9</v>
+        <v>417</v>
       </c>
       <c r="I12" t="n">
         <v>421.9397267801334</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K12" t="n">
-        <v>46.43</v>
+        <v>41.38</v>
       </c>
       <c r="L12" t="n">
         <v>3.07</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>13.1</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42929</v>
+        <v>42930</v>
       </c>
       <c r="H13" t="n">
-        <v>436.45</v>
+        <v>440</v>
       </c>
       <c r="I13" t="n">
         <v>439.0218926494348</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.66</v>
+        <v>-5.52</v>
       </c>
       <c r="L13" t="n">
-        <v>5.17</v>
+        <v>6.09</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.48</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H14" t="n">
-        <v>548.65</v>
+        <v>523.15</v>
       </c>
       <c r="I14" t="n">
         <v>529.162411405846</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K14" t="n">
-        <v>24.69</v>
+        <v>18.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.64</v>
       </c>
       <c r="M14" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="N14" t="n">
-        <v>4.01</v>
+        <v>4.65</v>
       </c>
       <c r="O14" t="n">
         <v>0.8100000000000001</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.32</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H15" t="n">
-        <v>531.25</v>
+        <v>535.35</v>
       </c>
       <c r="I15" t="n">
         <v>534.1987948254775</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.55</v>
+        <v>-2.33</v>
       </c>
       <c r="L15" t="n">
         <v>4.35</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.37</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43103</v>
+        <v>43104</v>
       </c>
       <c r="H16" t="n">
-        <v>509.95</v>
+        <v>506.25</v>
       </c>
       <c r="I16" t="n">
         <v>506.8765857116042</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.74</v>
+        <v>-5.44</v>
       </c>
       <c r="L16" t="n">
         <v>5.72</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.53</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43140</v>
+        <v>43143</v>
       </c>
       <c r="H17" t="n">
-        <v>505.95</v>
+        <v>523.55</v>
       </c>
       <c r="I17" t="n">
         <v>516.9744525294292</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K17" t="n">
-        <v>0.06</v>
+        <v>-3.42</v>
       </c>
       <c r="L17" t="n">
         <v>4.15</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.27</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43279</v>
+        <v>43280</v>
       </c>
       <c r="H18" t="n">
-        <v>584.8</v>
+        <v>582.1</v>
       </c>
       <c r="I18" t="n">
         <v>582.2154638099231</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K18" t="n">
-        <v>11.7</v>
+        <v>11.18</v>
       </c>
       <c r="L18" t="n">
         <v>8.32</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43292</v>
+        <v>43293</v>
       </c>
       <c r="H19" t="n">
-        <v>611.4</v>
+        <v>626.15</v>
       </c>
       <c r="I19" t="n">
         <v>624.3933980248785</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.03</v>
+        <v>-7.57</v>
       </c>
       <c r="L19" t="n">
-        <v>6.77</v>
+        <v>8.06</v>
       </c>
       <c r="M19" t="n">
         <v>0.67</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43343</v>
+        <v>43346</v>
       </c>
       <c r="H20" t="n">
-        <v>674.8</v>
+        <v>665.3</v>
       </c>
       <c r="I20" t="n">
         <v>670.7977868906233</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K20" t="n">
-        <v>7.77</v>
+        <v>6.25</v>
       </c>
       <c r="L20" t="n">
         <v>2.26</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.91</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43437</v>
+        <v>43438</v>
       </c>
       <c r="H21" t="n">
-        <v>599.95</v>
+        <v>607</v>
       </c>
       <c r="I21" t="n">
         <v>605.9693153757487</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K21" t="n">
-        <v>9.82</v>
+        <v>8.76</v>
       </c>
       <c r="L21" t="n">
         <v>2.81</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H22" t="n">
-        <v>632.15</v>
+        <v>605.1</v>
       </c>
       <c r="I22" t="n">
         <v>608.2810739529833</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K22" t="n">
-        <v>4.14</v>
+        <v>-0.31</v>
       </c>
       <c r="L22" t="n">
         <v>7.55</v>
@@ -1695,7 +1958,7 @@
         <v>4.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.98</v>
+        <v>4.28</v>
       </c>
       <c r="O22" t="n">
         <v>1.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>10</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43521</v>
+        <v>43522</v>
       </c>
       <c r="H23" t="n">
-        <v>633.35</v>
+        <v>645.25</v>
       </c>
       <c r="I23" t="n">
         <v>644.1269060712241</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.67</v>
+        <v>-6.64</v>
       </c>
       <c r="L23" t="n">
-        <v>5.63</v>
+        <v>7.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.52</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H24" t="n">
-        <v>843.55</v>
+        <v>759.3</v>
       </c>
       <c r="I24" t="n">
         <v>815.211630047903</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K24" t="n">
-        <v>30.73</v>
+        <v>17.68</v>
       </c>
       <c r="L24" t="n">
         <v>3.28</v>
@@ -1809,7 +2096,7 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>2.86</v>
+        <v>9.99</v>
       </c>
       <c r="O24" t="n">
         <v>1.88</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>13.89</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H25" t="n">
-        <v>718.85</v>
+        <v>769.35</v>
       </c>
       <c r="I25" t="n">
         <v>763.4129132396281</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K25" t="n">
-        <v>5.33</v>
+        <v>-1.32</v>
       </c>
       <c r="L25" t="n">
         <v>11.95</v>
@@ -1866,7 +2165,7 @@
         <v>3.84</v>
       </c>
       <c r="N25" t="n">
-        <v>6.64</v>
+        <v>7.03</v>
       </c>
       <c r="O25" t="n">
         <v>-9.99</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12.48</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H26" t="n">
-        <v>934.6</v>
+        <v>904.25</v>
       </c>
       <c r="I26" t="n">
         <v>911.4565847691117</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K26" t="n">
-        <v>21.48</v>
+        <v>17.53</v>
       </c>
       <c r="L26" t="n">
         <v>7.69</v>
@@ -1923,7 +2234,7 @@
         <v>0.51</v>
       </c>
       <c r="N26" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>7.03</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43843</v>
+        <v>43844</v>
       </c>
       <c r="H27" t="n">
-        <v>945.5</v>
+        <v>955.5</v>
       </c>
       <c r="I27" t="n">
         <v>952.7595872329857</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.56</v>
+        <v>-5.67</v>
       </c>
       <c r="L27" t="n">
-        <v>5.06</v>
+        <v>5.94</v>
       </c>
       <c r="M27" t="n">
         <v>3.88</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>5.73</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H28" t="n">
-        <v>944.15</v>
+        <v>894.75</v>
       </c>
       <c r="I28" t="n">
         <v>930.492665769366</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.19</v>
+        <v>-6.36</v>
       </c>
       <c r="L28" t="n">
-        <v>1.56</v>
+        <v>7.69</v>
       </c>
       <c r="M28" t="n">
         <v>0.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2.57</v>
+        <v>5.23</v>
       </c>
       <c r="O28" t="n">
         <v>1.06</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.46</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H29" t="n">
-        <v>476.3</v>
+        <v>518.45</v>
       </c>
       <c r="I29" t="n">
         <v>499.7048449224152</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K29" t="n">
-        <v>46.77</v>
+        <v>42.06</v>
       </c>
       <c r="L29" t="n">
         <v>9.99</v>
@@ -2094,7 +2441,7 @@
         <v>6.41</v>
       </c>
       <c r="N29" t="n">
-        <v>8.130000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="O29" t="n">
         <v>-5.23</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>21.41</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H30" t="n">
-        <v>623.4</v>
+        <v>602.7</v>
       </c>
       <c r="I30" t="n">
         <v>613.6113243737868</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K30" t="n">
-        <v>20.24</v>
+        <v>16.25</v>
       </c>
       <c r="L30" t="n">
         <v>8.529999999999999</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.54</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44117</v>
+        <v>44118</v>
       </c>
       <c r="H31" t="n">
-        <v>586.75</v>
+        <v>610</v>
       </c>
       <c r="I31" t="n">
         <v>606.601822131678</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K31" t="n">
-        <v>2.65</v>
+        <v>-1.21</v>
       </c>
       <c r="L31" t="n">
         <v>3.53</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H32" t="n">
-        <v>863.6</v>
+        <v>835.45</v>
       </c>
       <c r="I32" t="n">
         <v>857.3985485614551</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K32" t="n">
-        <v>41.57</v>
+        <v>36.96</v>
       </c>
       <c r="L32" t="n">
         <v>9.66</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>10.29</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H33" t="n">
-        <v>872.25</v>
+        <v>972.2</v>
       </c>
       <c r="I33" t="n">
         <v>921.4529032552118</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.4</v>
+        <v>-16.37</v>
       </c>
       <c r="L33" t="n">
-        <v>12.38</v>
+        <v>17.77</v>
       </c>
       <c r="M33" t="n">
         <v>0.97</v>
       </c>
       <c r="N33" t="n">
-        <v>6.82</v>
+        <v>11.46</v>
       </c>
       <c r="O33" t="n">
         <v>-3.26</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>17.3</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H34" t="n">
-        <v>952.5</v>
+        <v>943</v>
       </c>
       <c r="I34" t="n">
         <v>945.7423680530208</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.03</v>
+        <v>-3</v>
       </c>
       <c r="L34" t="n">
         <v>11.15</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>10.9</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44308</v>
+        <v>44309</v>
       </c>
       <c r="H35" t="n">
-        <v>985.4</v>
+        <v>991.65</v>
       </c>
       <c r="I35" t="n">
         <v>991.1902835169993</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.5</v>
+        <v>-5.16</v>
       </c>
       <c r="L35" t="n">
-        <v>5.47</v>
+        <v>7.56</v>
       </c>
       <c r="M35" t="n">
         <v>1.37</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.93</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H36" t="n">
-        <v>1792.1</v>
+        <v>1707.35</v>
       </c>
       <c r="I36" t="n">
         <v>1730.709694615129</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K36" t="n">
-        <v>80.72</v>
+        <v>72.17</v>
       </c>
       <c r="L36" t="n">
         <v>1.78</v>
@@ -2493,7 +2924,7 @@
         <v>2.28</v>
       </c>
       <c r="N36" t="n">
-        <v>3.42</v>
+        <v>4.73</v>
       </c>
       <c r="O36" t="n">
         <v>0.63</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8</v>
+      </c>
+      <c r="U36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>12.86</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H37" t="n">
-        <v>1713.55</v>
+        <v>1798.85</v>
       </c>
       <c r="I37" t="n">
         <v>1737.517680336591</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.36</v>
+        <v>-5.36</v>
       </c>
       <c r="L37" t="n">
         <v>6.25</v>
@@ -2550,7 +2993,7 @@
         <v>2.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3.51</v>
+        <v>4.98</v>
       </c>
       <c r="O37" t="n">
         <v>-4.73</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>10.61</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H38" t="n">
-        <v>1725.9</v>
+        <v>1633.5</v>
       </c>
       <c r="I38" t="n">
         <v>1708.574918060111</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.06</v>
+        <v>-9.19</v>
       </c>
       <c r="L38" t="n">
-        <v>5.05</v>
+        <v>9.83</v>
       </c>
       <c r="M38" t="n">
         <v>1.6</v>
       </c>
       <c r="N38" t="n">
-        <v>4.53</v>
+        <v>5.35</v>
       </c>
       <c r="O38" t="n">
         <v>4.98</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.55</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H39" t="n">
-        <v>1612.5</v>
+        <v>1637.1</v>
       </c>
       <c r="I39" t="n">
         <v>1628.166609424501</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K39" t="n">
-        <v>1.29</v>
+        <v>-0.22</v>
       </c>
       <c r="L39" t="n">
         <v>4.65</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.68</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44664</v>
+        <v>44669</v>
       </c>
       <c r="H40" t="n">
-        <v>1609</v>
+        <v>1582.7</v>
       </c>
       <c r="I40" t="n">
         <v>1585.226975972886</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.72</v>
+        <v>-3.32</v>
       </c>
       <c r="L40" t="n">
-        <v>2.57</v>
+        <v>4.38</v>
       </c>
       <c r="M40" t="n">
         <v>0.46</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.8</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44757</v>
+        <v>44760</v>
       </c>
       <c r="H41" t="n">
-        <v>1184</v>
+        <v>1225</v>
       </c>
       <c r="I41" t="n">
         <v>1213.869042955746</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K41" t="n">
-        <v>25.19</v>
+        <v>22.6</v>
       </c>
       <c r="L41" t="n">
         <v>1.6</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.59</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44859</v>
+        <v>44861</v>
       </c>
       <c r="H42" t="n">
-        <v>1658.55</v>
+        <v>1630.95</v>
       </c>
       <c r="I42" t="n">
         <v>1634.46633220215</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K42" t="n">
-        <v>35.39</v>
+        <v>33.14</v>
       </c>
       <c r="L42" t="n">
         <v>2.69</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44868</v>
+        <v>44869</v>
       </c>
       <c r="H43" t="n">
-        <v>1723.5</v>
+        <v>1800.7</v>
       </c>
       <c r="I43" t="n">
         <v>1781.94430303955</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.67</v>
+        <v>-10.41</v>
       </c>
       <c r="L43" t="n">
-        <v>6.23</v>
+        <v>10.67</v>
       </c>
       <c r="M43" t="n">
         <v>0.79</v>
       </c>
       <c r="N43" t="n">
-        <v>2.06</v>
+        <v>4.48</v>
       </c>
       <c r="O43" t="n">
         <v>-1.66</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.51</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44882</v>
+        <v>44883</v>
       </c>
       <c r="H44" t="n">
-        <v>1664.6</v>
+        <v>1654.4</v>
       </c>
       <c r="I44" t="n">
         <v>1655.786086248359</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.56</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>7.8</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>0.44</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.92</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44965</v>
+        <v>44966</v>
       </c>
       <c r="H45" t="n">
-        <v>1368.9</v>
+        <v>1400.25</v>
       </c>
       <c r="I45" t="n">
         <v>1392.397256068606</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K45" t="n">
-        <v>17.26</v>
+        <v>15.36</v>
       </c>
       <c r="L45" t="n">
         <v>1.22</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.94</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44995</v>
+        <v>44998</v>
       </c>
       <c r="H46" t="n">
-        <v>1328.85</v>
+        <v>1295.7</v>
       </c>
       <c r="I46" t="n">
         <v>1315.850809796686</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.1</v>
+        <v>-7.47</v>
       </c>
       <c r="L46" t="n">
-        <v>5.66</v>
+        <v>7.74</v>
       </c>
       <c r="M46" t="n">
         <v>0.93</v>
       </c>
       <c r="N46" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="O46" t="n">
         <v>2.29</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>9.5</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45028</v>
+        <v>45029</v>
       </c>
       <c r="H47" t="n">
-        <v>1321.55</v>
+        <v>1341.3</v>
       </c>
       <c r="I47" t="n">
         <v>1341.16012115165</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>-2</v>
+        <v>-3.52</v>
       </c>
       <c r="L47" t="n">
-        <v>3.51</v>
+        <v>3.88</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.49</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45139</v>
+        <v>45140</v>
       </c>
       <c r="H48" t="n">
-        <v>1572.35</v>
+        <v>1527</v>
       </c>
       <c r="I48" t="n">
         <v>1559.016858366</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K48" t="n">
-        <v>17.23</v>
+        <v>13.84</v>
       </c>
       <c r="L48" t="n">
         <v>2.59</v>
@@ -3177,7 +3752,7 @@
         <v>1.2</v>
       </c>
       <c r="N48" t="n">
-        <v>1.84</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
         <v>1.49</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.83</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45181</v>
+        <v>45182</v>
       </c>
       <c r="H49" t="n">
-        <v>1542.45</v>
+        <v>1552.8</v>
       </c>
       <c r="I49" t="n">
         <v>1551.800830387749</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.01</v>
+        <v>-1.69</v>
       </c>
       <c r="L49" t="n">
         <v>2.97</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.81</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H50" t="n">
-        <v>1611.45</v>
+        <v>1560</v>
       </c>
       <c r="I50" t="n">
         <v>1568.403278549479</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K50" t="n">
-        <v>3.78</v>
+        <v>0.46</v>
       </c>
       <c r="L50" t="n">
         <v>2.5</v>
@@ -3291,7 +3890,7 @@
         <v>1.47</v>
       </c>
       <c r="N50" t="n">
-        <v>1.83</v>
+        <v>3.19</v>
       </c>
       <c r="O50" t="n">
         <v>0.67</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>8.27</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="H51" t="n">
-        <v>1653.5</v>
+        <v>1673.5</v>
       </c>
       <c r="I51" t="n">
         <v>1661.474685821823</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.99</v>
+        <v>-7.28</v>
       </c>
       <c r="L51" t="n">
-        <v>6.73</v>
+        <v>7.69</v>
       </c>
       <c r="M51" t="n">
         <v>2.4</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>6.23</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45303</v>
+        <v>45306</v>
       </c>
       <c r="H52" t="n">
-        <v>1651.9</v>
+        <v>1632.4</v>
       </c>
       <c r="I52" t="n">
         <v>1642.050657086183</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.29</v>
+        <v>-2.46</v>
       </c>
       <c r="L52" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="M52" t="n">
         <v>1.06</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.87</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H53" t="n">
-        <v>1646</v>
+        <v>1656.55</v>
       </c>
       <c r="I53" t="n">
         <v>1647.251190322328</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.83</v>
+        <v>-1.48</v>
       </c>
       <c r="L53" t="n">
         <v>2.55</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.47</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H54" t="n">
-        <v>1618.5</v>
+        <v>1593.9</v>
       </c>
       <c r="I54" t="n">
         <v>1611.92599004014</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.3</v>
+        <v>-3.78</v>
       </c>
       <c r="L54" t="n">
-        <v>2.73</v>
+        <v>4.06</v>
       </c>
       <c r="M54" t="n">
         <v>1.57</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.43</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H55" t="n">
-        <v>1609.55</v>
+        <v>1651.25</v>
       </c>
       <c r="I55" t="n">
         <v>1631.493904598509</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.98</v>
+        <v>-3.6</v>
       </c>
       <c r="L55" t="n">
         <v>8.23</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.51</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H56" t="n">
-        <v>1623.45</v>
+        <v>1567.7</v>
       </c>
       <c r="I56" t="n">
         <v>1568.203485453587</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.68</v>
+        <v>-5.06</v>
       </c>
       <c r="L56" t="n">
         <v>5.65</v>
       </c>
       <c r="M56" t="n">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="N56" t="n">
-        <v>2.45</v>
+        <v>3.43</v>
       </c>
       <c r="O56" t="n">
         <v>2.59</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.93</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45526</v>
+        <v>45527</v>
       </c>
       <c r="H57" t="n">
-        <v>1625.7</v>
+        <v>1639.9</v>
       </c>
       <c r="I57" t="n">
         <v>1632.424505044871</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.7</v>
+        <v>-4.61</v>
       </c>
       <c r="L57" t="n">
-        <v>3.97</v>
+        <v>4.93</v>
       </c>
       <c r="M57" t="n">
         <v>1.29</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.07</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45572</v>
+        <v>45573</v>
       </c>
       <c r="H58" t="n">
-        <v>1879.3</v>
+        <v>1838.15</v>
       </c>
       <c r="I58" t="n">
         <v>1860.983052431904</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K58" t="n">
-        <v>14.6</v>
+        <v>12.09</v>
       </c>
       <c r="L58" t="n">
         <v>1.02</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.57</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="H59" t="n">
-        <v>1576.4</v>
+        <v>1700.65</v>
       </c>
       <c r="I59" t="n">
         <v>1657.037880521233</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K59" t="n">
-        <v>14.24</v>
+        <v>7.48</v>
       </c>
       <c r="L59" t="n">
         <v>3.13</v>
@@ -3804,7 +4511,7 @@
         <v>1.07</v>
       </c>
       <c r="N59" t="n">
-        <v>2.09</v>
+        <v>7.88</v>
       </c>
       <c r="O59" t="n">
         <v>-2.19</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>10.19</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H60" t="n">
-        <v>1912.3</v>
+        <v>1852.65</v>
       </c>
       <c r="I60" t="n">
         <v>1854.826754362641</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K60" t="n">
-        <v>12.45</v>
+        <v>8.94</v>
       </c>
       <c r="L60" t="n">
         <v>7.31</v>
       </c>
       <c r="M60" t="n">
-        <v>1.81</v>
+        <v>4.04</v>
       </c>
       <c r="N60" t="n">
         <v>3.5</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.02</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H61" t="n">
-        <v>1969.2</v>
+        <v>2035.3</v>
       </c>
       <c r="I61" t="n">
         <v>2019.778379316404</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.29</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>7.09</v>
+        <v>10.1</v>
       </c>
       <c r="M61" t="n">
         <v>2.02</v>
       </c>
       <c r="N61" t="n">
-        <v>2.73</v>
+        <v>3.36</v>
       </c>
       <c r="O61" t="n">
         <v>-3.12</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H62" t="n">
-        <v>1948</v>
+        <v>1916.3</v>
       </c>
       <c r="I62" t="n">
         <v>1943.121611943916</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.29</v>
+        <v>-5.85</v>
       </c>
       <c r="L62" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="M62" t="n">
         <v>2.36</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="H63" t="n">
-        <v>2008.4</v>
+        <v>2025.3</v>
       </c>
       <c r="I63" t="n">
         <v>2015.817052902767</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.81</v>
+        <v>-5.69</v>
       </c>
       <c r="L63" t="n">
-        <v>6.13</v>
+        <v>6.4</v>
       </c>
       <c r="M63" t="n">
         <v>1.3</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.74</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H64" t="n">
-        <v>2073.2</v>
+        <v>2063.2</v>
       </c>
       <c r="I64" t="n">
         <v>2063.240386396625</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K64" t="n">
-        <v>2.37</v>
+        <v>1.87</v>
       </c>
       <c r="L64" t="n">
         <v>2.83</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.65</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="H65" t="n">
-        <v>2027</v>
+        <v>2037.1</v>
       </c>
       <c r="I65" t="n">
         <v>2031.075471017388</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K65" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="L65" t="n">
         <v>3.08</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.11</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H66" t="n">
-        <v>1993.4</v>
+        <v>1941.9</v>
       </c>
       <c r="I66" t="n">
         <v>1959.638822053442</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.15</v>
+        <v>-4.67</v>
       </c>
       <c r="L66" t="n">
-        <v>2.48</v>
+        <v>5.4</v>
       </c>
       <c r="M66" t="n">
-        <v>0.91</v>
+        <v>2.18</v>
       </c>
       <c r="N66" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="O66" t="n">
         <v>0.5</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.82</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H67" t="n">
-        <v>1684.4</v>
+        <v>1784.6</v>
       </c>
       <c r="I67" t="n">
         <v>1776.296664444716</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K67" t="n">
-        <v>13.26</v>
+        <v>8.1</v>
       </c>
       <c r="L67" t="n">
         <v>2.48</v>
       </c>
       <c r="M67" t="n">
-        <v>2.89</v>
+        <v>3.98</v>
       </c>
       <c r="N67" t="n">
-        <v>2.45</v>
+        <v>5.95</v>
       </c>
       <c r="O67" t="n">
         <v>-2.58</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>10.42</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H68" t="n">
-        <v>1734.4</v>
+        <v>1709.8</v>
       </c>
       <c r="I68" t="n">
         <v>1710.441297915325</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.81</v>
+        <v>-4.19</v>
       </c>
       <c r="L68" t="n">
         <v>5.09</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>7.15</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="H69" t="n">
-        <v>1750.2</v>
+        <v>1787.3</v>
       </c>
       <c r="I69" t="n">
         <v>1756.698220096707</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.36</v>
+        <v>-4.53</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>5.38</v>
       </c>
       <c r="M69" t="n">
         <v>1.47</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.57</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H70" t="n">
-        <v>1970</v>
+        <v>1938.6</v>
       </c>
       <c r="I70" t="n">
         <v>1953.529757719474</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K70" t="n">
-        <v>10.22</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L70" t="n">
         <v>2.56</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>35</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.2</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.5</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.19</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12.43</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80.72</v>
+        <v>72.17</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.13</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.35</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.38</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="25">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.76</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="27">
@@ -9669,7 +10528,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.81</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="28">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
